--- a/diseases/d163/2020-2025.xlsx
+++ b/diseases/d163/2020-2025.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>9</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.08692556028232069</v>
       </c>
@@ -1705,9 +1699,6 @@
       <c r="O7" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.0185898709184428</v>
       </c>
@@ -2101,9 +2092,6 @@
       <c r="O9" t="n">
         <v>5</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.04829197793462262</v>
       </c>
@@ -2645,9 +2633,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -3041,9 +3026,6 @@
       <c r="O14" t="n">
         <v>4</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.03863358234769809</v>
       </c>
@@ -3437,9 +3419,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -3833,9 +3812,6 @@
       <c r="O18" t="n">
         <v>2</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.01931679117384904</v>
       </c>
@@ -4377,9 +4353,6 @@
       <c r="O21" t="n">
         <v>1</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.0185898709184428</v>
       </c>
@@ -4773,9 +4746,6 @@
       <c r="O23" t="n">
         <v>6</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.05795037352154713</v>
       </c>
@@ -5169,9 +5139,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -5565,9 +5532,6 @@
       <c r="O27" t="n">
         <v>3</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.02897518676077357</v>
       </c>
@@ -6109,9 +6073,6 @@
       <c r="O30" t="n">
         <v>1</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.0185898709184428</v>
       </c>
@@ -6505,9 +6466,6 @@
       <c r="O32" t="n">
         <v>1</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.009658395586924521</v>
       </c>
@@ -6901,9 +6859,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -7297,9 +7252,6 @@
       <c r="O36" t="n">
         <v>7</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.06760876910847165</v>
       </c>
@@ -7841,9 +7793,6 @@
       <c r="O39" t="n">
         <v>1</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.0185898709184428</v>
       </c>
@@ -8237,9 +8186,6 @@
       <c r="O41" t="n">
         <v>1</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.009658395586924521</v>
       </c>
@@ -8781,9 +8727,6 @@
       <c r="O44" t="n">
         <v>2</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.03717974183688559</v>
       </c>
@@ -9177,9 +9120,6 @@
       <c r="O46" t="n">
         <v>3</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.02897518676077357</v>
       </c>
@@ -9721,9 +9661,6 @@
       <c r="O49" t="n">
         <v>2</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.03717974183688559</v>
       </c>
@@ -10117,9 +10054,6 @@
       <c r="O51" t="n">
         <v>8</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.07726716469539617</v>
       </c>
@@ -10513,9 +10447,6 @@
       <c r="O53" t="n">
         <v>4</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.07435948367377118</v>
       </c>
@@ -10909,9 +10840,6 @@
       <c r="O55" t="n">
         <v>12</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.1159007470430943</v>
       </c>
@@ -11453,9 +11381,6 @@
       <c r="O58" t="n">
         <v>4</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.07396325930566436</v>
       </c>
@@ -11849,9 +11774,6 @@
       <c r="O60" t="n">
         <v>15</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.1440073985241066</v>
       </c>
@@ -12393,9 +12315,6 @@
       <c r="O63" t="n">
         <v>3</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.05547244447924827</v>
       </c>
@@ -12789,9 +12708,6 @@
       <c r="O65" t="n">
         <v>11</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.1056054255843448</v>
       </c>
@@ -13185,9 +13101,6 @@
       <c r="O67" t="n">
         <v>5</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.09245407413208045</v>
       </c>
@@ -13581,9 +13494,6 @@
       <c r="O69" t="n">
         <v>7</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.06720345264458306</v>
       </c>
@@ -14125,9 +14035,6 @@
       <c r="O72" t="n">
         <v>2</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.03698162965283218</v>
       </c>
@@ -14521,9 +14428,6 @@
       <c r="O74" t="n">
         <v>10</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.09600493234940438</v>
       </c>
@@ -15065,9 +14969,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -15461,9 +15362,6 @@
       <c r="O79" t="n">
         <v>22</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.2112108511686897</v>
       </c>
@@ -16005,9 +15903,6 @@
       <c r="O82" t="n">
         <v>2</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.03698162965283218</v>
       </c>
@@ -16401,9 +16296,6 @@
       <c r="O84" t="n">
         <v>8</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.07680394587952351</v>
       </c>
@@ -16797,9 +16689,6 @@
       <c r="O86" t="n">
         <v>1</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.01849081482641609</v>
       </c>
@@ -17193,9 +17082,6 @@
       <c r="O88" t="n">
         <v>14</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.1344069052891661</v>
       </c>
@@ -17737,9 +17623,6 @@
       <c r="O91" t="n">
         <v>3</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.05547244447924827</v>
       </c>
@@ -18133,9 +18016,6 @@
       <c r="O93" t="n">
         <v>24</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.2304118376385705</v>
       </c>
@@ -18529,9 +18409,6 @@
       <c r="O95" t="n">
         <v>1</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.01849081482641609</v>
       </c>
@@ -18925,9 +18802,6 @@
       <c r="O97" t="n">
         <v>22</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.2112108511686897</v>
       </c>
@@ -19321,9 +19195,6 @@
       <c r="O99" t="n">
         <v>5</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.09245407413208045</v>
       </c>
@@ -19717,9 +19588,6 @@
       <c r="O101" t="n">
         <v>23</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.2208113444036301</v>
       </c>
@@ -20113,9 +19981,6 @@
       <c r="O103" t="n">
         <v>6</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.1109448889584965</v>
       </c>
@@ -20509,9 +20374,6 @@
       <c r="O105" t="n">
         <v>34</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.3264167699879749</v>
       </c>
@@ -20905,9 +20767,6 @@
       <c r="O107" t="n">
         <v>6</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.1109448889584965</v>
       </c>
@@ -21301,9 +21160,6 @@
       <c r="O109" t="n">
         <v>87</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.8352429114398182</v>
       </c>
@@ -21697,9 +21553,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -22093,9 +21946,6 @@
       <c r="O113" t="n">
         <v>64</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.6102597246317416</v>
       </c>
@@ -22489,9 +22339,6 @@
       <c r="O115" t="n">
         <v>3</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.05497726094672859</v>
       </c>
@@ -22885,9 +22732,6 @@
       <c r="O117" t="n">
         <v>57</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.543512567250145</v>
       </c>
@@ -23281,9 +23125,6 @@
       <c r="O119" t="n">
         <v>2</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.03665150729781906</v>
       </c>
@@ -23677,9 +23518,6 @@
       <c r="O121" t="n">
         <v>71</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.6770068820133384</v>
       </c>
@@ -24073,9 +23911,6 @@
       <c r="O123" t="n">
         <v>4</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.07330301459563812</v>
       </c>
@@ -24469,9 +24304,6 @@
       <c r="O125" t="n">
         <v>55</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.524441950855403</v>
       </c>
@@ -24865,9 +24697,6 @@
       <c r="O127" t="n">
         <v>1</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.01832575364890953</v>
       </c>
@@ -25261,9 +25090,6 @@
       <c r="O129" t="n">
         <v>40</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.3814123278948385</v>
       </c>
@@ -25657,9 +25483,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -26053,9 +25876,6 @@
       <c r="O133" t="n">
         <v>35</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.3337357869079837</v>
       </c>
@@ -26449,9 +26269,6 @@
       <c r="O135" t="n">
         <v>1</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.01832575364890953</v>
       </c>
@@ -26845,9 +26662,6 @@
       <c r="O137" t="n">
         <v>15</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.1430296229605645</v>
       </c>
@@ -27241,9 +27055,6 @@
       <c r="O139" t="n">
         <v>1</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.01832575364890953</v>
       </c>
@@ -27637,9 +27448,6 @@
       <c r="O141" t="n">
         <v>22</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0.2097767803421612</v>
       </c>
@@ -28033,9 +27841,6 @@
       <c r="O143" t="n">
         <v>1</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.01832575364890953</v>
       </c>
@@ -28429,9 +28234,6 @@
       <c r="O145" t="n">
         <v>25</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.238382704934274</v>
       </c>
@@ -28825,9 +28627,6 @@
       <c r="O147" t="n">
         <v>4</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0.07330301459563812</v>
       </c>
@@ -29221,9 +29020,6 @@
       <c r="O149" t="n">
         <v>18</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.1716355475526773</v>
       </c>
@@ -29617,9 +29413,6 @@
       <c r="O151" t="n">
         <v>1</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.01832575364890953</v>
       </c>
@@ -30013,9 +29806,6 @@
       <c r="O153" t="n">
         <v>27</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.257453321329016</v>
       </c>
@@ -30409,9 +30199,6 @@
       <c r="O155" t="n">
         <v>2</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.03665150729781906</v>
       </c>
@@ -30805,9 +30592,6 @@
       <c r="O157" t="n">
         <v>26</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.247918013131645</v>
       </c>
@@ -31201,9 +30985,6 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0</v>
       </c>
@@ -31597,9 +31378,6 @@
       <c r="O161" t="n">
         <v>22</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0.2085012795344432</v>
       </c>
@@ -31993,9 +31771,6 @@
       <c r="O163" t="n">
         <v>2</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.03623735248453254</v>
       </c>
@@ -32389,9 +32164,6 @@
       <c r="O165" t="n">
         <v>20</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.1895466177585847</v>
       </c>
@@ -32785,9 +32557,6 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0</v>
       </c>
@@ -33181,9 +32950,6 @@
       <c r="O169" t="n">
         <v>27</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0.2558879339740894</v>
       </c>
@@ -33577,9 +33343,6 @@
       <c r="O171" t="n">
         <v>1</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.01811867624226627</v>
       </c>
@@ -33973,9 +33736,6 @@
       <c r="O173" t="n">
         <v>21</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.199023948646514</v>
       </c>
@@ -34369,9 +34129,6 @@
       <c r="O175" t="n">
         <v>1</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.01811867624226627</v>
       </c>
@@ -34765,9 +34522,6 @@
       <c r="O177" t="n">
         <v>17</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0.161114625094797</v>
       </c>
@@ -35161,9 +34915,6 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
@@ -35557,9 +35308,6 @@
       <c r="O181" t="n">
         <v>7</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0.06634131621550465</v>
       </c>
@@ -35953,9 +35701,6 @@
       <c r="O183" t="n">
         <v>2</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0.03623735248453254</v>
       </c>
@@ -36349,9 +36094,6 @@
       <c r="O185" t="n">
         <v>0</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0</v>
       </c>
@@ -36745,9 +36487,6 @@
       <c r="O187" t="n">
         <v>2</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0.03623735248453254</v>
       </c>
@@ -37141,9 +36880,6 @@
       <c r="O189" t="n">
         <v>11</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0.1042506397672216</v>
       </c>
@@ -37537,9 +37273,6 @@
       <c r="O191" t="n">
         <v>2</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0.03623735248453254</v>
       </c>
@@ -37933,9 +37666,6 @@
       <c r="O193" t="n">
         <v>2</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.01895466177585847</v>
       </c>
@@ -38329,9 +38059,6 @@
       <c r="O195" t="n">
         <v>1</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0.01811867624226627</v>
       </c>
@@ -38725,9 +38452,6 @@
       <c r="O197" t="n">
         <v>6</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0.05686398532757541</v>
       </c>
@@ -39121,9 +38845,6 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0</v>
       </c>
@@ -39517,9 +39238,6 @@
       <c r="O201" t="n">
         <v>8</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0.07581864710343389</v>
       </c>
@@ -39913,9 +39631,6 @@
       <c r="O203" t="n">
         <v>4</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0.07247470496906508</v>
       </c>
@@ -40309,9 +40024,6 @@
       <c r="O205" t="n">
         <v>14</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0.1326826324310093</v>
       </c>
@@ -40705,9 +40417,6 @@
       <c r="O207" t="n">
         <v>5</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0.08965940186419828</v>
       </c>
@@ -41101,9 +40810,6 @@
       <c r="O209" t="n">
         <v>8</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>0.07542189831449969</v>
       </c>
@@ -41497,9 +41203,6 @@
       <c r="O211" t="n">
         <v>2</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0.03586376074567932</v>
       </c>
@@ -41893,9 +41596,6 @@
       <c r="O213" t="n">
         <v>14</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0.1319883220503745</v>
       </c>
@@ -42289,9 +41989,6 @@
       <c r="O215" t="n">
         <v>1</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0.01793188037283966</v>
       </c>
@@ -42685,9 +42382,6 @@
       <c r="O217" t="n">
         <v>3</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0.02828321186793739</v>
       </c>
@@ -43081,9 +42775,6 @@
       <c r="O219" t="n">
         <v>2</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>0.03586376074567932</v>
       </c>
@@ -43477,9 +43168,6 @@
       <c r="O221" t="n">
         <v>9</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0.08484963560381216</v>
       </c>
@@ -43873,9 +43561,6 @@
       <c r="O223" t="n">
         <v>0</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0</v>
       </c>
@@ -44269,9 +43954,6 @@
       <c r="O225" t="n">
         <v>7</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0.06599416102518724</v>
       </c>
@@ -44665,9 +44347,6 @@
       <c r="O227" t="n">
         <v>2</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0.03586376074567932</v>
       </c>
@@ -45061,9 +44740,6 @@
       <c r="O229" t="n">
         <v>5</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0.04713868644656231</v>
       </c>
@@ -45457,9 +45133,6 @@
       <c r="O231" t="n">
         <v>0</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0</v>
       </c>
@@ -45853,9 +45526,6 @@
       <c r="O233" t="n">
         <v>3</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0.02828321186793739</v>
       </c>
@@ -46249,9 +45919,6 @@
       <c r="O235" t="n">
         <v>0</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>0</v>
       </c>
@@ -46645,9 +46312,6 @@
       <c r="O237" t="n">
         <v>6</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>0.05656642373587478</v>
       </c>
@@ -47041,9 +46705,6 @@
       <c r="O239" t="n">
         <v>1</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0.01793188037283966</v>
       </c>
@@ -47437,9 +47098,6 @@
       <c r="O241" t="n">
         <v>2</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>0.01885547457862492</v>
       </c>
@@ -47833,9 +47491,6 @@
       <c r="O243" t="n">
         <v>6</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0.1075912822370379</v>
       </c>
@@ -48229,9 +47884,6 @@
       <c r="O245" t="n">
         <v>4</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0.03771094915724985</v>
       </c>
@@ -48625,9 +48277,6 @@
       <c r="O247" t="n">
         <v>3</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="R247" t="n">
         <v>0.05379564111851897</v>
       </c>
@@ -49021,9 +48670,6 @@
       <c r="O249" t="n">
         <v>12</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="R249" t="n">
         <v>0.1131328474717496</v>
       </c>
@@ -49417,9 +49063,6 @@
       <c r="O251" t="n">
         <v>5</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="R251" t="n">
         <v>0.08965940186419828</v>
       </c>
@@ -49813,9 +49456,6 @@
       <c r="O253" t="n">
         <v>10</v>
       </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
       <c r="R253" t="n">
         <v>0.09427737289312463</v>
       </c>
@@ -50209,9 +49849,6 @@
       <c r="O255" t="n">
         <v>4</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0.07113550584724966</v>
       </c>
@@ -50605,9 +50242,6 @@
       <c r="O257" t="n">
         <v>8</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="R257" t="n">
         <v>0.07507061564379668</v>
       </c>
@@ -51001,9 +50635,6 @@
       <c r="O259" t="n">
         <v>4</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0.07113550584724966</v>
       </c>
@@ -51397,9 +51028,6 @@
       <c r="O261" t="n">
         <v>10</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="R261" t="n">
         <v>0.09383826955474586</v>
       </c>
@@ -51793,9 +51421,6 @@
       <c r="O263" t="n">
         <v>1</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0.01778387646181242</v>
       </c>
@@ -52189,9 +51814,6 @@
       <c r="O265" t="n">
         <v>2</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0.01876765391094917</v>
       </c>
@@ -52585,9 +52207,6 @@
       <c r="O267" t="n">
         <v>5</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0.08891938230906209</v>
       </c>
@@ -52981,9 +52600,6 @@
       <c r="O269" t="n">
         <v>2</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0.01876765391094917</v>
       </c>
@@ -53377,9 +52993,6 @@
       <c r="O271" t="n">
         <v>2</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>0.03556775292362483</v>
       </c>
@@ -53773,9 +53386,6 @@
       <c r="O273" t="n">
         <v>6</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0.05630296173284752</v>
       </c>
@@ -54169,9 +53779,6 @@
       <c r="O275" t="n">
         <v>1</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0.01778387646181242</v>
       </c>
@@ -54565,9 +54172,6 @@
       <c r="O277" t="n">
         <v>9</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>0.08445444259927126</v>
       </c>
@@ -54961,9 +54565,6 @@
       <c r="O279" t="n">
         <v>1</v>
       </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
       <c r="R279" t="n">
         <v>0.01778387646181242</v>
       </c>
@@ -55357,9 +54958,6 @@
       <c r="O281" t="n">
         <v>7</v>
       </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
       <c r="R281" t="n">
         <v>0.0656867886883221</v>
       </c>
@@ -55753,9 +55351,6 @@
       <c r="O283" t="n">
         <v>3</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>0.05335162938543725</v>
       </c>
@@ -56149,9 +55744,6 @@
       <c r="O285" t="n">
         <v>17</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0.159525058243068</v>
       </c>
@@ -56545,9 +56137,6 @@
       <c r="O287" t="n">
         <v>1</v>
       </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
       <c r="R287" t="n">
         <v>0.01778387646181242</v>
       </c>
@@ -56941,9 +56530,6 @@
       <c r="O289" t="n">
         <v>9</v>
       </c>
-      <c r="Q289" t="n">
-        <v>0</v>
-      </c>
       <c r="R289" t="n">
         <v>0.08445444259927126</v>
       </c>
@@ -57337,9 +56923,6 @@
       <c r="O291" t="n">
         <v>4</v>
       </c>
-      <c r="Q291" t="n">
-        <v>0</v>
-      </c>
       <c r="R291" t="n">
         <v>0.07113550584724966</v>
       </c>
@@ -57733,9 +57316,6 @@
       <c r="O293" t="n">
         <v>13</v>
       </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
       <c r="R293" t="n">
         <v>0.1219897504211696</v>
       </c>
@@ -58129,9 +57709,6 @@
       <c r="O295" t="n">
         <v>4</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0.07113550584724966</v>
       </c>
@@ -58525,9 +58102,6 @@
       <c r="O297" t="n">
         <v>18</v>
       </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
       <c r="R297" t="n">
         <v>0.1689088851985425</v>
       </c>
@@ -58921,9 +58495,6 @@
       <c r="O299" t="n">
         <v>4</v>
       </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
       <c r="R299" t="n">
         <v>0.07113550584724966</v>
       </c>
@@ -59316,9 +58887,6 @@
       </c>
       <c r="O301" t="n">
         <v>30</v>
-      </c>
-      <c r="Q301" t="n">
-        <v>0</v>
       </c>
       <c r="R301" t="n">
         <v>0.2815148086642376</v>
